--- a/naver-place-crawler/results_nail/전주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/전주_네일샵.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="Q2" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="R2" t="n">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일너에게 효자점</t>
+          <t>네일너에게 전북대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wlwjd1891@naver.com</t>
+          <t>perfectgogo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1308-0190</t>
+          <t>0507-1419-6644</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 문학대4길 28-8 1층</t>
+          <t>전북 전주시 덕진구 기린대로 508 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.to_u</t>
+          <t>https://www.instagram.com/nail.to_u</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ml0l</t>
+          <t>https://talk.naver.com/ct/wd2lllr</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1686</v>
+        <v>481</v>
       </c>
       <c r="Q3" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>1796</v>
+        <v>516</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1354879635</t>
+          <t>1775087669</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354879635</t>
+          <t>https://m.place.naver.com/place/1775087669</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일너에게 전북대점</t>
+          <t>레푸스 전주효자점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>perfectgogo@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1419-6644</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 기린대로 508 1층</t>
+          <t>전북 전주시 완산구 마전2길 13 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.to_u</t>
+          <t>https://blog.naver.com/refussjj</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wd2lllr</t>
+          <t>https://talk.naver.com/ct/w45wxo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>476</v>
+        <v>1261</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="R4" t="n">
-        <v>511</v>
+        <v>1428</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1775087669</t>
+          <t>1468552297</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1775087669</t>
+          <t>https://m.place.naver.com/place/1468552297</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -854,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일이예쁘다 문학본점</t>
+          <t>네일너에게 효자점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dkgkgk1229@naver.com</t>
+          <t>wlwjd1891@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1392-3803</t>
+          <t>0507-1308-0190</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 문학대4길 29 1층 네일이예쁘다</t>
+          <t>전북 전주시 완산구 문학대4길 28-8 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.yeppeuda</t>
+          <t>http://instagram.com/nail.to_u</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43oxx</t>
+          <t>https://talk.naver.com/ct/w4ml0l</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>653</v>
+        <v>1694</v>
       </c>
       <c r="Q5" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="R5" t="n">
-        <v>785</v>
+        <v>1804</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1631577872</t>
+          <t>1354879635</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1631577872</t>
+          <t>https://m.place.naver.com/place/1354879635</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -952,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>티나네일 전주송천</t>
+          <t>우린네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hello_tinanail@naver.com</t>
+          <t>frlend815@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1398-7458</t>
+          <t>0507-1359-2330</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 오송1길 37-5 105호</t>
+          <t>전북 전주시 덕진구 명륜4길 10-5 1층 우린네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tinanail2013</t>
+          <t>https://www.instagram.com/woorin_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xc22</t>
+          <t>https://talk.naver.com/ct/w4sg8p</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>477</v>
+        <v>1347</v>
       </c>
       <c r="Q6" t="n">
-        <v>397</v>
+        <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>874</v>
+        <v>1365</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>32890783</t>
+          <t>1252147879</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32890783</t>
+          <t>https://m.place.naver.com/place/1252147879</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1050,25 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 전주혁신점</t>
+          <t>티나네일 전주송천</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>refussjj@naver.com</t>
+          <t>hello_tinanail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1398-7458</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
+          <t>전북 전주시 덕진구 오송1길 37-5 105호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
+          <t>https://www.instagram.com/tinanail2013</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ayx2</t>
+          <t>https://talk.naver.com/ct/w5xc22</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1004</v>
+        <v>477</v>
       </c>
       <c r="Q7" t="n">
-        <v>297</v>
+        <v>395</v>
       </c>
       <c r="R7" t="n">
-        <v>1301</v>
+        <v>872</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1122,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1726250171</t>
+          <t>32890783</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726250171</t>
+          <t>https://m.place.naver.com/place/32890783</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유어네일</t>
+          <t>깡언니네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hjrang0606@naver.com</t>
+          <t>changjowan@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1486-1120</t>
+          <t>0507-1326-2605</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 구룡1길 19 101호</t>
+          <t>전북 전주시 완산구 문학대6길 11 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/n.your_nail</t>
+          <t>https://www.instagram.com/kkangsister</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tkex</t>
+          <t>https://talk.naver.com/ct/w44mqw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>149</v>
+        <v>251</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1513094096</t>
+          <t>37101779</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1513094096</t>
+          <t>https://m.place.naver.com/place/37101779</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>살롱네일그대와</t>
+          <t>레푸스 전주혁신점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjdwlswn5742@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>063-273-6688</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서곡3길 3 1층 살롱네일그대와</t>
+          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/banara9</t>
+          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1285,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc6010</t>
+          <t>https://talk.naver.com/ct/w4ayx2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>1016</v>
       </c>
       <c r="Q9" t="n">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="R9" t="n">
-        <v>123</v>
+        <v>1314</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1092132145</t>
+          <t>1726250171</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092132145</t>
+          <t>https://m.place.naver.com/place/1726250171</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오부띠끄</t>
+          <t>살롱네일그대와</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansgml8705@naver.com</t>
+          <t>wjdwlswn5742@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1425-0195</t>
+          <t>063-273-6688</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 송천중앙로 225 파인트리몰 4층 419호,오부띠끄네일(송천동)</t>
+          <t>전북 전주시 완산구 서곡3길 3 1층 살롱네일그대와</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ohboutique_nail</t>
+          <t>http://www.instagram.com/banara9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1387,12 +1383,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w428nx</t>
+          <t>https://talk.naver.com/ct/wc6010</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1401,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="R10" t="n">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1412,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1926381485</t>
+          <t>1092132145</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926381485</t>
+          <t>https://m.place.naver.com/place/1092132145</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1438,39 +1434,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유주네일</t>
+          <t>오부띠끄</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>seoinyoung@naver.com</t>
+          <t>ansgml8705@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1419-2046</t>
+          <t>0507-1425-0195</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 메너머2길 29-14 1층 101호</t>
+          <t>전북 전주시 덕진구 송천중앙로 225 파인트리몰 4층 419호,오부띠끄네일(송천동)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/528837</t>
+          <t>https://www.instagram.com/ohboutique_nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,12 +1481,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4a9hi</t>
+          <t>https://talk.naver.com/ct/w428nx</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="R11" t="n">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1045747409</t>
+          <t>1926381485</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045747409</t>
+          <t>https://m.place.naver.com/place/1926381485</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/전주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/전주_네일샵.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="Q2" t="n">
         <v>63</v>
       </c>
       <c r="R2" t="n">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="Q4" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R4" t="n">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="Q5" t="n">
         <v>110</v>
       </c>
       <c r="R5" t="n">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="Q6" t="n">
         <v>18</v>
       </c>
       <c r="R6" t="n">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1046,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>티나네일 전주송천</t>
+          <t>레푸스 전주혁신점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hello_tinanail@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1398-7458</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 오송1길 37-5 105호</t>
+          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tinanail2013</t>
+          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xc22</t>
+          <t>https://talk.naver.com/ct/w4ayx2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>477</v>
+        <v>1022</v>
       </c>
       <c r="Q7" t="n">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="R7" t="n">
-        <v>872</v>
+        <v>1320</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32890783</t>
+          <t>1726250171</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32890783</t>
+          <t>https://m.place.naver.com/place/1726250171</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q8" t="n">
         <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1230,7 +1226,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1242,25 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>레푸스 전주혁신점</t>
+          <t>네일해봄</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>refussjj@naver.com</t>
+          <t>eruriee@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1331-4336</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
+          <t>전북 전주시 덕진구 사근1길 71 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
+          <t>https://www.instagram.com/h_bom_nail?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1280,14 +1280,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ayx2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1299,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1016</v>
+        <v>219</v>
       </c>
       <c r="Q9" t="n">
-        <v>298</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>1314</v>
+        <v>235</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1726250171</t>
+          <t>1872434604</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726250171</t>
+          <t>https://m.place.naver.com/place/1872434604</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1336,29 +1332,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>살롱네일그대와</t>
+          <t>던네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjdwlswn5742@naver.com</t>
+          <t>nakang1801@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>063-273-6688</t>
+          <t>0507-1336-0258</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서곡3길 3 1층 살롱네일그대와</t>
+          <t>전북 전주시 완산구 범안2길 10 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/banara9</t>
+          <t>https://www.instagram.com/dawn_nail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1378,14 +1374,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc6010</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="Q10" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1412,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1092132145</t>
+          <t>1602780360</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092132145</t>
+          <t>https://m.place.naver.com/place/1602780360</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1434,29 +1426,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오부띠끄</t>
+          <t>네일베베</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ansgml8705@naver.com</t>
+          <t>jisunlove2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1425-0195</t>
+          <t>0507-1376-5468</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 송천중앙로 225 파인트리몰 4층 419호,오부띠끄네일(송천동)</t>
+          <t>전북 전주시 완산구 효자천변1길 36-12 1층 101호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ohboutique_nail</t>
+          <t>https://www.instagram.com/nail_be.be/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,12 +1473,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w428nx</t>
+          <t>https://talk.naver.com/ct/wceeth9</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1495,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="Q11" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>148</v>
+        <v>239</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,17 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1926381485</t>
+          <t>2078679649</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1926381485</t>
+          <t>https://m.place.naver.com/place/2078679649</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/전주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/전주_네일샵.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아띠네일 신시가지점</t>
+          <t>레푸스 전주효자점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0507-1402-6605</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 홍산남로 18 삼흥빌딩 1층</t>
+          <t>전북 전주시 완산구 마전2길 13 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/_attinail</t>
+          <t>https://blog.naver.com/refussjj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +597,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45wxo</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>962</v>
+        <v>1266</v>
       </c>
       <c r="Q2" t="n">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="R2" t="n">
-        <v>1025</v>
+        <v>1434</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1104785143</t>
+          <t>1468552297</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1104785143</t>
+          <t>https://m.place.naver.com/place/1468552297</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -756,25 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>레푸스 전주효자점</t>
+          <t>네일너에게 효자점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>refussjj@naver.com</t>
+          <t>wlwjd1891@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0507-1308-0190</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 마전2길 13 1층</t>
+          <t>전북 전주시 완산구 문학대4길 28-8 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refussjj</t>
+          <t>http://instagram.com/nail.to_u</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45wxo</t>
+          <t>https://talk.naver.com/ct/w4ml0l</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -813,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1266</v>
+        <v>1695</v>
       </c>
       <c r="Q4" t="n">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="R4" t="n">
-        <v>1434</v>
+        <v>1805</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1468552297</t>
+          <t>1354879635</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468552297</t>
+          <t>https://m.place.naver.com/place/1354879635</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일너에게 효자점</t>
+          <t>아띠네일 신시가지점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wlwjd1891@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1308-0190</t>
+          <t>0507-1402-6605</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 문학대4길 28-8 1층</t>
+          <t>전북 전주시 완산구 홍산남로 18 삼흥빌딩 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.to_u</t>
+          <t>http://www.instagram.com/_attinail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,14 +896,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ml0l</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1695</v>
+        <v>962</v>
       </c>
       <c r="Q5" t="n">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="R5" t="n">
-        <v>1805</v>
+        <v>1025</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1354879635</t>
+          <t>1104785143</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1354879635</t>
+          <t>https://m.place.naver.com/place/1104785143</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -948,29 +948,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>우린네일</t>
+          <t>네일데이유 전북대점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>frlend815@naver.com</t>
+          <t>gowls001@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1359-2330</t>
+          <t>0507-1398-5517</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 명륜4길 10-5 1층 우린네일</t>
+          <t>전북 전주시 덕진구 명륜4길 11-3 네일데이유</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woorin_nail</t>
+          <t>https://www.instagram.com/nail_day.u</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sg8p</t>
+          <t>https://talk.naver.com/ct/w5iyvx</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1351</v>
+        <v>1948</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>1369</v>
+        <v>1969</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1252147879</t>
+          <t>1921651501</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252147879</t>
+          <t>https://m.place.naver.com/place/1921651501</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,25 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 전주혁신점</t>
+          <t>티나네일 전주송천</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>refussjj@naver.com</t>
+          <t>hello_tinanail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1398-7458</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
+          <t>전북 전주시 덕진구 오송1길 37-5 105호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
+          <t>https://www.instagram.com/tinanail2013</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1089,12 +1093,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ayx2</t>
+          <t>https://talk.naver.com/ct/w5xc22</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1022</v>
+        <v>477</v>
       </c>
       <c r="Q7" t="n">
-        <v>298</v>
+        <v>395</v>
       </c>
       <c r="R7" t="n">
-        <v>1320</v>
+        <v>872</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1726250171</t>
+          <t>32890783</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726250171</t>
+          <t>https://m.place.naver.com/place/32890783</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,29 +1144,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>깡언니네일</t>
+          <t>레푸스 전주혁신점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>changjowan@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1326-2605</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 문학대6길 11 1층</t>
+          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkangsister</t>
+          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44mqw</t>
+          <t>https://talk.naver.com/ct/w4ayx2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>214</v>
+        <v>1023</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>298</v>
       </c>
       <c r="R8" t="n">
-        <v>253</v>
+        <v>1321</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37101779</t>
+          <t>1726250171</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37101779</t>
+          <t>https://m.place.naver.com/place/1726250171</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일해봄</t>
+          <t>깡언니네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>eruriee@naver.com</t>
+          <t>changjowan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1331-4336</t>
+          <t>0507-1326-2605</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 사근1길 71 1층</t>
+          <t>전북 전주시 완산구 문학대6길 11 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/h_bom_nail?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/kkangsister</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1280,10 +1280,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44mqw</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Q9" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1314,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1872434604</t>
+          <t>37101779</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872434604</t>
+          <t>https://m.place.naver.com/place/37101779</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1426,29 +1430,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일베베</t>
+          <t>살롱네일그대와</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jisunlove2@naver.com</t>
+          <t>wjdwlswn5742@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1376-5468</t>
+          <t>063-273-6688</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 효자천변1길 36-12 1층 101호</t>
+          <t>전북 전주시 완산구 서곡3길 3 1층 살롱네일그대와</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_be.be/</t>
+          <t>http://www.instagram.com/banara9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wceeth9</t>
+          <t>https://talk.naver.com/ct/wc6010</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1487,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="R11" t="n">
-        <v>239</v>
+        <v>122</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1502,12 +1506,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2078679649</t>
+          <t>1092132145</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078679649</t>
+          <t>https://m.place.naver.com/place/1092132145</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_nail/전주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/전주_네일샵.xlsx
@@ -422,12 +422,12 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -582,7 +582,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refussjj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="Q2" t="n">
         <v>168</v>
       </c>
       <c r="R2" t="n">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.to_u</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q3" t="n">
         <v>35</v>
       </c>
       <c r="R3" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.to_u</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="Q5" t="n">
         <v>63</v>
       </c>
       <c r="R5" t="n">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1009,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="Q6" t="n">
         <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1046,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>티나네일 전주송천</t>
+          <t>레푸스 전주혁신점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hello_tinanail@naver.com</t>
+          <t>refussjj@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1398-7458</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 오송1길 37-5 105호</t>
+          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tinanail2013</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1078,7 +1074,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xc22</t>
+          <t>https://talk.naver.com/ct/w4ayx2</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1107,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>477</v>
+        <v>1023</v>
       </c>
       <c r="Q7" t="n">
-        <v>395</v>
+        <v>298</v>
       </c>
       <c r="R7" t="n">
-        <v>872</v>
+        <v>1321</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32890783</t>
+          <t>1726250171</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32890783</t>
+          <t>https://m.place.naver.com/place/1726250171</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1144,25 +1140,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>레푸스 전주혁신점</t>
+          <t>깡언니네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>refussjj@naver.com</t>
+          <t>changjowan@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1326-2605</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>전북 전주시 덕진구 만성로 73 LK타워 3층</t>
+          <t>전북 전주시 완산구 문학대6길 11 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtube.com/@jeonju-refuss?si=6z3qYNMv5OqwTxbb</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ayx2</t>
+          <t>https://talk.naver.com/ct/w44mqw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1023</v>
+        <v>214</v>
       </c>
       <c r="Q8" t="n">
-        <v>298</v>
+        <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>1321</v>
+        <v>253</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1726250171</t>
+          <t>37101779</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1726250171</t>
+          <t>https://m.place.naver.com/place/37101779</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>깡언니네일</t>
+          <t>네일또바</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>changjowan@naver.com</t>
+          <t>nail_ddoba@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1326-2605</t>
+          <t>0507-1330-4327</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 문학대6길 11 1층</t>
+          <t>전북 전주시 완산구 봉곡로 43 1층 101호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kkangsister</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44mqw</t>
+          <t>https://talk.naver.com/ct/w46gmj</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="R9" t="n">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37101779</t>
+          <t>1555436109</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37101779</t>
+          <t>https://m.place.naver.com/place/1555436109</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,29 +1336,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>던네일</t>
+          <t>네일해봄</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nakang1801@naver.com</t>
+          <t>jh801017@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1336-0258</t>
+          <t>0507-1331-4336</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 범안2길 10 1층</t>
+          <t>전북 전주시 덕진구 사근1길 71 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dawn_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1602780360</t>
+          <t>1872434604</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602780360</t>
+          <t>https://m.place.naver.com/place/1872434604</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1430,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>살롱네일그대와</t>
+          <t>던네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wjdwlswn5742@naver.com</t>
+          <t>nakang1801@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>063-273-6688</t>
+          <t>0507-1336-0258</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>전북 전주시 완산구 서곡3길 3 1층 살롱네일그대와</t>
+          <t>전북 전주시 완산구 범안2길 10 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/banara9</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1472,14 +1472,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc6010</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1487,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="Q11" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1502,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1092132145</t>
+          <t>1602780360</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092132145</t>
+          <t>https://m.place.naver.com/place/1602780360</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
